--- a/data-rights-register/air-shopping-register-example.xlsx
+++ b/data-rights-register/air-shopping-register-example.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -511,7 +511,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>3. A derived dataset inherits the strictest rights of its parents. The aggregated insights (DS-DER-002) are the licensable product, and they depend on questions still open above them.</t>
+          <t>3. A derived dataset inherits the strictest rights of its parents. The aggregated insights (DS-DER-002) are the product we sell, and they depend on questions still open above them.</t>
         </is>
       </c>
     </row>
@@ -525,7 +525,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>5. legal_confirmed is blank on every row. Only Legal sets it. Until then pricing may not quote any of these rights.</t>
+          <t>5. legal_confirmed is blank on every row. Only Legal sets it. Until then pricing can price products that rely on these rows only as Provisional, and cannot release them for quoting.</t>
         </is>
       </c>
     </row>
@@ -537,10 +537,17 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr"/>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>7. Every row here is a right WE HOLD on the dataset: what we may do with it. What a customer is granted on a product is set separately in the price book (conferred_right) and is checked against these rows through the coverage table in the price-book-builder skill.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Sheets: Rights_Matrix_View, Datasets, Use_Rights, Fields, Evidence, Open_Questions, Change_Log, Vocabulary.</t>
         </is>
@@ -2788,7 +2795,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Licensable for the customer's own use if aggregation and anonymization standards are met (Q-0004).</t>
+          <t>We may use it in our own products and services if aggregation and anonymization standards are met (Q-0004).</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -2820,7 +2827,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Outputs must stay market-level; no airline or agency identifiable.</t>
+          <t>We may supply outputs to customers only if they stay market-level; no airline or agency identifiable.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -3064,10 +3071,10 @@
       <formula1>=Vocabulary!$E$2:$E$10</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Vocabulary!$F$2:$F$5</formula1>
+      <formula1>=Vocabulary!$G$2:$G$5</formula1>
     </dataValidation>
     <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Vocabulary!$G$2:$G$3</formula1>
+      <formula1>=Vocabulary!$H$2:$H$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5071,7 +5078,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Vocabulary!$H$2:$H$7</formula1>
+      <formula1>=Vocabulary!$I$2:$I$7</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5304,7 +5311,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>May licensees redistribute or embed the insights in their own products, and under what conditions?</t>
+          <t>May we let customers redistribute the insights or embed them in their own products, and under what conditions?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -5446,13 +5453,13 @@
   </sheetData>
   <dataValidations count="3">
     <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Vocabulary!$I$2:$I$6</formula1>
+      <formula1>=Vocabulary!$J$2:$J$6</formula1>
     </dataValidation>
     <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Vocabulary!$J$2:$J$4</formula1>
+      <formula1>=Vocabulary!$K$2:$K$4</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Vocabulary!$K$2:$K$4</formula1>
+      <formula1>=Vocabulary!$L$2:$L$4</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5669,7 +5676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5683,6 +5690,7 @@
     <col width="34" customWidth="1" min="9" max="9"/>
     <col width="34" customWidth="1" min="10" max="10"/>
     <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5713,30 +5721,35 @@
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
+          <t>use_right_meaning_held</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
           <t>right_status</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>yes_no</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>document_type</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>owner_role</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>priority</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>question_status</t>
         </is>
@@ -5770,30 +5783,35 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>internal_use: we may use the data in our own operations</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>Granted</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Supplier agreement</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Legal</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5827,30 +5845,35 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>internal_analytics_shared_outputs: we may share outputs we derive (reports, aggregates) outside our company, including with customers</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>Conditional</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Customer agreement</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Answered</t>
         </is>
@@ -5884,25 +5907,30 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>display_to_third_parties: we may show the data or substantial extracts to customers and partners</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>Prohibited</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Terms of service</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Data engineering</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -5931,15 +5959,20 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>redistribution_resale: we may pass on or resell the data itself</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Policy</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
@@ -5961,12 +5994,17 @@
           <t>derivative_data_product</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>derivative_data_product: we may build and sell a new data product from it</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Sales operations</t>
         </is>
@@ -5988,7 +6026,12 @@
           <t>ai_training</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ai_training: we may train or pre-train a model on it</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
@@ -6000,6 +6043,11 @@
           <t>ai_fine_tuning</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ai_fine_tuning: we may fine-tune a model on it</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="E9" t="inlineStr">
@@ -6007,11 +6055,21 @@
           <t>ai_retrieval_grounding</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>ai_retrieval_grounding: we may supply it to a model or agent at query time</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="E10" t="inlineStr">
         <is>
           <t>ai_evaluation</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ai_evaluation: we may benchmark or evaluate a model with it</t>
         </is>
       </c>
     </row>
